--- a/JsonConverter/ExcelFiles/Arcana.xlsx
+++ b/JsonConverter/ExcelFiles/Arcana.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="15945" windowHeight="24345" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="15765" windowHeight="11715" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Sheet1" sheetId="1" r:id="rId4"/>
@@ -21,10 +21,187 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="80">
   <x:si>
+    <x:t>세계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여사제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>악마</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATK</x:t>
   </x:si>
   <x:si>
-    <x:t>공격력</x:t>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>황제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>죽음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>별</x:t>
+  </x:si>
+  <x:si>
+    <x:t>탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>힘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>절제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심판</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>점수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여황제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은둔자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교황</x:t>
+  </x:si>
+  <x:si>
+    <x:t>태양</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Effect</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Score</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매달린 남자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>효과 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카드 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카드 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>운명의 수레바퀴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조화와 관계. 타인과의 깊은 공명, 혹은 화합을 의미합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무구함과 새로운 시작. 아무것도 모르는 순수함을 상징합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전진과 승리. 고난이 있어도 멈추지 않고 돌진하는 의지입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>권위와 질서. 혼란을 잠재우기 위해 강압적일 수 있는 단호한 통제력을 상징합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유혹과 구속. 내면의 공포나 욕망에 굴복하여 어둠의 힘을 거리낌 없이 사용합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조절과 화합. 과하지 않게 에너지를 나누고 갈등을 중재하는 평화로운 수단입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인내와 용기. 무력이 아닌 부드러운 힘으로 거친 세상을 길들이는 내면의 강함입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종결과 재생. 낡은 자아를 버리고 완전히 새로운 모습으로 거듭나는 극단적 변화입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불안과 혼돈. 실체를 알 수 없는 공포 앞에서 경계심을 늦추지 않는 상태입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>붕괴와 재난. 공들여 쌓아온 것이 무너질 때 느껴지는 허망함과 충격을 뜻합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>풍요와 생명. 척박한 지하 세계에서도 생명을 틔우고 주변을 보살피는 자비입니다.</x:t>
   </x:si>
   <x:si>
     <x:t>완성된 조화. 모든 여정을 끝내고 빛 아래 완전한 존재로 거듭납니다.</x:t>
@@ -36,229 +213,52 @@
     <x:t>희망과 정화. 어둠 속에서도 잃지 않는 순수한 믿음과 치유의 빛입니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Arcana_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>운명의 수레바퀴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종결과 재생. 낡은 자아를 버리고 완전히 새로운 모습으로 거듭나는 극단적 변화입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유혹과 구속. 내면의 공포나 욕망에 굴복하여 어둠의 힘을 거리낌 없이 사용합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조절과 화합. 과하지 않게 에너지를 나누고 갈등을 중재하는 평화로운 수단입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>권위와 질서. 혼란을 잠재우기 위해 강압적일 수 있는 단호한 통제력을 상징합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인내와 용기. 무력이 아닌 부드러운 힘으로 거친 세상을 길들이는 내면의 강함입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불안과 혼돈. 실체를 알 수 없는 공포 앞에서 경계심을 늦추지 않는 상태입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>붕괴와 재난. 공들여 쌓아온 것이 무너질 때 느껴지는 허망함과 충격을 뜻합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>풍요와 생명. 척박한 지하 세계에서도 생명을 틔우고 주변을 보살피는 자비입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전진과 승리. 고난이 있어도 멈추지 않고 돌진하는 의지입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조화와 관계. 타인과의 깊은 공명, 혹은 화합을 의미합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무구함과 새로운 시작. 아무것도 모르는 순수함을 상징합니다.</x:t>
+    <x:t>직관과 지혜. 보이지 않는 진실을 꿰뚫어 보며 내면의 소리에 귀를 기울입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>균형과 인과. 죄에 대한 정당한 처벌을 내리며, 감정보다 이성을 중시합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생명력과 진실. 모든 비밀을 밝히고 밝은 에너지를 발산하는 긍정적 힘입니다.</x:t>
   </x:si>
   <x:si>
     <x:t>고독과 성찰. 타인과의 관계를 끊고 오로지 자신의 목적만을 위해 침잠합니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>균형과 인과. 죄에 대한 정당한 처벌을 내리며, 감정보다 이성을 중시합니다.</x:t>
+    <x:t>창조와 기술. 무언가를 고치거나 새로운 길을 만들어내는 능력을 뜻합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전통과 신념. 규칙을 준수하며 옳고 그름에 대한 도덕적 잣대를 제시합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>결말과 보상. 지금까지의 행적에 대해 마지막 책임을 지고 과오를 인정합니다.</x:t>
   </x:si>
   <x:si>
     <x:t>희생과 인내. 더 큰 목적을 위해 현재의 고통을 묵묵히 받아들이는 태도입니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>생명력과 진실. 모든 비밀을 밝히고 밝은 에너지를 발산하는 긍정적 힘입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>결말과 보상. 지금까지의 행적에 대해 마지막 책임을 지고 과오를 인정합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>창조와 기술. 무언가를 고치거나 새로운 길을 만들어내는 능력을 뜻합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직관과 지혜. 보이지 않는 진실을 꿰뚫어 보며 내면의 소리에 귀를 기울입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전통과 신념. 규칙을 준수하며 옳고 그름에 대한 도덕적 잣대를 제시합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>절제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>광대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>점수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심판</x:t>
-  </x:si>
-  <x:si>
-    <x:t>죽음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>황제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>별</x:t>
-  </x:si>
-  <x:si>
-    <x:t>악마</x:t>
-  </x:si>
-  <x:si>
-    <x:t>힘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여사제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>태양</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여황제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은둔자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>교황</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카드 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카드 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Effect</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Score</x:t>
-  </x:si>
-  <x:si>
-    <x:t>효과 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매달린 남자</x:t>
+    <x:t>Arcana_4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_9</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -346,7 +346,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="11">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -1042,661 +1045,661 @@
   <x:dimension ref="A1:G67"/>
   <x:sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.550000000000001"/>
   <x:cols>
-    <x:col min="1" max="1" width="10.5546875" style="4" customWidth="1"/>
-    <x:col min="2" max="2" width="13.5546875" style="4" customWidth="1"/>
-    <x:col min="3" max="3" width="66.33203125" style="4" customWidth="1"/>
-    <x:col min="5" max="5" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="6" max="6" width="8.88671875" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="10.5546875" style="5" customWidth="1"/>
+    <x:col min="2" max="2" width="13.5546875" style="5" customWidth="1"/>
+    <x:col min="3" max="3" width="66.33203125" style="5" customWidth="1"/>
+    <x:col min="5" max="5" width="8.88671875" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="6" max="6" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6">
-      <x:c r="A1" s="5" t="s">
+      <x:c r="A1" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:6">
+      <x:c r="A2" s="6" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:6">
+      <x:c r="A3" s="7" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:6" s="9" customFormat="1">
+      <x:c r="A4" s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D4" s="10"/>
+      <x:c r="E4" s="10">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" s="10">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:6">
+      <x:c r="A5" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D5" s="6"/>
+      <x:c r="E5" s="6">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F5" s="6">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:6">
+      <x:c r="A6" s="6" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D6" s="6"/>
+      <x:c r="E6" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" s="6">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:6">
+      <x:c r="A7" s="6" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F7" s="6">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:6">
+      <x:c r="A8" s="6" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C1" s="5" t="s">
+      <x:c r="B8" s="6" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F8" s="6">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:6">
+      <x:c r="A9" s="6" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C9" s="8" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D9" s="6"/>
+      <x:c r="E9" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F9" s="6">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:6">
+      <x:c r="A10" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C10" s="8" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D10" s="6"/>
+      <x:c r="E10" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" s="6">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:6">
+      <x:c r="A11" s="6" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C11" s="8" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D11" s="6"/>
+      <x:c r="E11" s="6">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F11" s="6">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:7" s="4" customFormat="1">
+      <x:c r="A12" s="6" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="8" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D12" s="6"/>
+      <x:c r="E12" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F12" s="6">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G12" s="1"/>
+    </x:row>
+    <x:row r="13" spans="1:7" s="4" customFormat="1">
+      <x:c r="A13" s="6" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="8" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D13" s="6"/>
+      <x:c r="E13" s="6">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F13" s="6">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G13" s="1"/>
+    </x:row>
+    <x:row r="14" spans="1:6">
+      <x:c r="A14" s="6" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D14" s="6"/>
+      <x:c r="E14" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F14" s="6">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:6">
+      <x:c r="A15" s="6" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C15" s="8" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D15" s="6"/>
+      <x:c r="E15" s="6">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F15" s="6">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:6">
+      <x:c r="A16" s="6" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="8" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D16" s="6"/>
+      <x:c r="E16" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F16" s="6">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:6">
+      <x:c r="A17" s="6" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C17" s="8" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D17" s="6"/>
+      <x:c r="E17" s="6">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F17" s="6">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:6">
+      <x:c r="A18" s="6" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C18" s="8" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D18" s="6"/>
+      <x:c r="E18" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F18" s="6">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:6">
+      <x:c r="A19" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C19" s="8" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E1" s="5" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F1" s="5" t="s">
+      <x:c r="D19" s="6"/>
+      <x:c r="E19" s="6">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F19" s="6">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:6">
+      <x:c r="A20" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="8" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D20" s="6"/>
+      <x:c r="E20" s="6">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F20" s="6">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:6">
+      <x:c r="A21" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="8" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D21" s="6"/>
+      <x:c r="E21" s="6">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6">
-      <x:c r="A2" s="5" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B2" s="5" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C2" s="5" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D2" s="5" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E2" s="5" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F2" s="5" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6">
-      <x:c r="A3" s="6" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B3" s="6" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C3" s="6" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D3" s="6" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E3" s="6" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="s">
+      <x:c r="F21" s="6">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:6">
+      <x:c r="A22" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C22" s="8" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D22" s="6"/>
+      <x:c r="E22" s="6">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F22" s="6">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:6">
+      <x:c r="A23" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C23" s="8" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D23" s="6"/>
+      <x:c r="E23" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F23" s="6">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:6">
+      <x:c r="A24" s="6" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C24" s="8" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D24" s="6"/>
+      <x:c r="E24" s="6">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="F24" s="6">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:6">
+      <x:c r="A25" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="s">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:6" s="8" customFormat="1">
-      <x:c r="A4" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B4" s="9" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D4" s="9"/>
-      <x:c r="E4" s="9">
+      <x:c r="C25" s="8" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E25" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F4" s="9">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:6">
-      <x:c r="A5" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C5" s="7" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D5" s="5"/>
-      <x:c r="E5" s="5">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F5" s="5">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:6">
-      <x:c r="A6" s="5" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D6" s="5"/>
-      <x:c r="E6" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F6" s="5">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:6">
-      <x:c r="A7" s="5" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D7" s="5"/>
-      <x:c r="E7" s="5">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F7" s="5">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:6">
-      <x:c r="A8" s="5" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D8" s="5"/>
-      <x:c r="E8" s="5">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F8" s="5">
+      <x:c r="F25" s="6">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:6">
-      <x:c r="A9" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C9" s="7" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D9" s="5"/>
-      <x:c r="E9" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F9" s="5">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:6">
-      <x:c r="A10" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C10" s="7" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D10" s="5"/>
-      <x:c r="E10" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F10" s="5">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:6">
-      <x:c r="A11" s="5" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D11" s="5"/>
-      <x:c r="E11" s="5">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F11" s="5">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:7" s="3" customFormat="1">
-      <x:c r="A12" s="5" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B12" s="5" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C12" s="7" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D12" s="5"/>
-      <x:c r="E12" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F12" s="5">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G12"/>
-    </x:row>
-    <x:row r="13" spans="1:7" s="3" customFormat="1">
-      <x:c r="A13" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B13" s="5" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C13" s="7" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D13" s="5"/>
-      <x:c r="E13" s="5">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F13" s="5">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G13"/>
-    </x:row>
-    <x:row r="14" spans="1:6">
-      <x:c r="A14" s="5" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B14" s="5" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="7" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="5"/>
-      <x:c r="E14" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F14" s="5">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:6">
-      <x:c r="A15" s="5" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B15" s="5" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C15" s="7" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D15" s="5"/>
-      <x:c r="E15" s="5">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F15" s="5">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:6">
-      <x:c r="A16" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B16" s="5" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C16" s="7" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D16" s="5"/>
-      <x:c r="E16" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F16" s="5">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:6">
-      <x:c r="A17" s="5" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B17" s="5" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C17" s="7" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D17" s="5"/>
-      <x:c r="E17" s="5">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F17" s="5">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:6">
-      <x:c r="A18" s="5" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B18" s="5" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C18" s="7" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D18" s="5"/>
-      <x:c r="E18" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F18" s="5">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:6">
-      <x:c r="A19" s="5" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B19" s="5" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C19" s="7" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D19" s="5"/>
-      <x:c r="E19" s="5">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F19" s="5">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:6">
-      <x:c r="A20" s="5" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B20" s="5" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C20" s="7" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D20" s="5"/>
-      <x:c r="E20" s="5">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F20" s="5">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:6">
-      <x:c r="A21" s="5" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B21" s="5" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C21" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="5"/>
-      <x:c r="E21" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F21" s="5">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:6">
-      <x:c r="A22" s="5" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B22" s="5" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C22" s="7" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D22" s="5"/>
-      <x:c r="E22" s="5">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F22" s="5">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:6">
-      <x:c r="A23" s="5" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B23" s="5" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C23" s="7" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D23" s="5"/>
-      <x:c r="E23" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F23" s="5">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:6">
-      <x:c r="A24" s="5" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B24" s="5" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C24" s="7" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D24" s="5"/>
-      <x:c r="E24" s="5">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F24" s="5">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:6">
-      <x:c r="A25" s="5" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B25" s="5" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C25" s="7" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E25">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F25" s="5">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
     <x:row r="26" spans="1:6">
-      <x:c r="A26" s="5"/>
-      <x:c r="B26" s="5"/>
-      <x:c r="E26"/>
-      <x:c r="F26" s="5"/>
+      <x:c r="A26" s="6"/>
+      <x:c r="B26" s="6"/>
+      <x:c r="E26" s="1"/>
+      <x:c r="F26" s="6"/>
     </x:row>
     <x:row r="27" spans="1:6">
-      <x:c r="A27" s="5"/>
-      <x:c r="B27" s="5"/>
-      <x:c r="C27" s="7"/>
-      <x:c r="E27"/>
-      <x:c r="F27" s="5"/>
+      <x:c r="A27" s="6"/>
+      <x:c r="B27" s="6"/>
+      <x:c r="C27" s="8"/>
+      <x:c r="E27" s="1"/>
+      <x:c r="F27" s="6"/>
     </x:row>
     <x:row r="28" spans="1:5">
-      <x:c r="A28" s="5"/>
-      <x:c r="B28" s="5"/>
-      <x:c r="C28" s="7"/>
-      <x:c r="E28"/>
+      <x:c r="A28" s="6"/>
+      <x:c r="B28" s="6"/>
+      <x:c r="C28" s="8"/>
+      <x:c r="E28" s="1"/>
     </x:row>
     <x:row r="29" spans="1:2">
-      <x:c r="A29" s="5"/>
-      <x:c r="B29" s="5"/>
+      <x:c r="A29" s="6"/>
+      <x:c r="B29" s="6"/>
     </x:row>
     <x:row r="30" spans="1:3">
-      <x:c r="A30" s="5"/>
-      <x:c r="B30" s="5"/>
-      <x:c r="C30" s="7"/>
+      <x:c r="A30" s="6"/>
+      <x:c r="B30" s="6"/>
+      <x:c r="C30" s="8"/>
     </x:row>
     <x:row r="31" spans="1:2">
-      <x:c r="A31" s="5"/>
-      <x:c r="B31" s="5"/>
+      <x:c r="A31" s="6"/>
+      <x:c r="B31" s="6"/>
     </x:row>
     <x:row r="32" spans="1:3">
-      <x:c r="A32" s="5"/>
-      <x:c r="B32" s="5"/>
-      <x:c r="C32" s="7"/>
+      <x:c r="A32" s="6"/>
+      <x:c r="B32" s="6"/>
+      <x:c r="C32" s="8"/>
     </x:row>
     <x:row r="33" spans="1:2">
-      <x:c r="A33" s="5"/>
-      <x:c r="B33" s="5"/>
+      <x:c r="A33" s="6"/>
+      <x:c r="B33" s="6"/>
     </x:row>
     <x:row r="34" spans="1:2">
-      <x:c r="A34" s="5"/>
-      <x:c r="B34" s="5"/>
+      <x:c r="A34" s="6"/>
+      <x:c r="B34" s="6"/>
     </x:row>
     <x:row r="35" spans="1:3">
-      <x:c r="A35" s="5"/>
-      <x:c r="B35" s="5"/>
-      <x:c r="C35" s="7"/>
+      <x:c r="A35" s="6"/>
+      <x:c r="B35" s="6"/>
+      <x:c r="C35" s="8"/>
     </x:row>
     <x:row r="36" spans="1:3">
-      <x:c r="A36" s="5"/>
-      <x:c r="B36" s="5"/>
-      <x:c r="C36" s="7"/>
+      <x:c r="A36" s="6"/>
+      <x:c r="B36" s="6"/>
+      <x:c r="C36" s="8"/>
     </x:row>
     <x:row r="37" spans="1:2">
-      <x:c r="A37" s="5"/>
-      <x:c r="B37" s="5"/>
+      <x:c r="A37" s="6"/>
+      <x:c r="B37" s="6"/>
     </x:row>
     <x:row r="38" spans="1:2">
-      <x:c r="A38" s="5"/>
-      <x:c r="B38" s="5"/>
+      <x:c r="A38" s="6"/>
+      <x:c r="B38" s="6"/>
     </x:row>
     <x:row r="39" spans="1:2">
-      <x:c r="A39" s="5"/>
-      <x:c r="B39" s="5"/>
+      <x:c r="A39" s="6"/>
+      <x:c r="B39" s="6"/>
     </x:row>
     <x:row r="40" spans="1:3">
-      <x:c r="A40" s="5"/>
-      <x:c r="B40" s="5"/>
-      <x:c r="C40" s="7"/>
+      <x:c r="A40" s="6"/>
+      <x:c r="B40" s="6"/>
+      <x:c r="C40" s="8"/>
     </x:row>
     <x:row r="41" spans="1:3">
-      <x:c r="A41" s="5"/>
-      <x:c r="B41" s="5"/>
-      <x:c r="C41" s="7"/>
+      <x:c r="A41" s="6"/>
+      <x:c r="B41" s="6"/>
+      <x:c r="C41" s="8"/>
     </x:row>
     <x:row r="42" spans="1:2">
-      <x:c r="A42" s="5"/>
-      <x:c r="B42" s="5"/>
+      <x:c r="A42" s="6"/>
+      <x:c r="B42" s="6"/>
     </x:row>
     <x:row r="43" spans="1:2">
-      <x:c r="A43" s="5"/>
-      <x:c r="B43" s="5"/>
+      <x:c r="A43" s="6"/>
+      <x:c r="B43" s="6"/>
     </x:row>
     <x:row r="44" spans="1:2">
-      <x:c r="A44" s="5"/>
-      <x:c r="B44" s="5"/>
+      <x:c r="A44" s="6"/>
+      <x:c r="B44" s="6"/>
     </x:row>
     <x:row r="45" spans="1:3">
-      <x:c r="A45" s="5"/>
-      <x:c r="B45" s="5"/>
-      <x:c r="C45" s="7"/>
+      <x:c r="A45" s="6"/>
+      <x:c r="B45" s="6"/>
+      <x:c r="C45" s="8"/>
     </x:row>
     <x:row r="46" spans="1:2">
-      <x:c r="A46" s="5"/>
-      <x:c r="B46" s="5"/>
+      <x:c r="A46" s="6"/>
+      <x:c r="B46" s="6"/>
     </x:row>
     <x:row r="47" spans="1:2">
-      <x:c r="A47" s="5"/>
-      <x:c r="B47" s="5"/>
+      <x:c r="A47" s="6"/>
+      <x:c r="B47" s="6"/>
     </x:row>
     <x:row r="48" spans="1:3">
-      <x:c r="A48" s="5"/>
-      <x:c r="B48" s="5"/>
-      <x:c r="C48" s="7"/>
+      <x:c r="A48" s="6"/>
+      <x:c r="B48" s="6"/>
+      <x:c r="C48" s="8"/>
     </x:row>
     <x:row r="49" spans="1:1">
-      <x:c r="A49" s="5"/>
+      <x:c r="A49" s="6"/>
     </x:row>
     <x:row r="50" spans="1:3">
-      <x:c r="A50" s="5"/>
-      <x:c r="B50" s="5"/>
-      <x:c r="C50" s="7"/>
+      <x:c r="A50" s="6"/>
+      <x:c r="B50" s="6"/>
+      <x:c r="C50" s="8"/>
     </x:row>
     <x:row r="51" spans="1:2">
-      <x:c r="A51" s="5"/>
-      <x:c r="B51" s="5"/>
+      <x:c r="A51" s="6"/>
+      <x:c r="B51" s="6"/>
     </x:row>
     <x:row r="52" spans="1:3">
-      <x:c r="A52" s="5"/>
-      <x:c r="B52" s="5"/>
-      <x:c r="C52" s="7"/>
+      <x:c r="A52" s="6"/>
+      <x:c r="B52" s="6"/>
+      <x:c r="C52" s="8"/>
     </x:row>
     <x:row r="53" spans="1:2">
-      <x:c r="A53" s="5"/>
-      <x:c r="B53" s="5"/>
+      <x:c r="A53" s="6"/>
+      <x:c r="B53" s="6"/>
     </x:row>
     <x:row r="54" spans="1:3">
-      <x:c r="A54" s="5"/>
-      <x:c r="B54" s="5"/>
-      <x:c r="C54" s="7"/>
+      <x:c r="A54" s="6"/>
+      <x:c r="B54" s="6"/>
+      <x:c r="C54" s="8"/>
     </x:row>
     <x:row r="55" spans="1:2">
-      <x:c r="A55" s="5"/>
-      <x:c r="B55" s="5"/>
+      <x:c r="A55" s="6"/>
+      <x:c r="B55" s="6"/>
     </x:row>
     <x:row r="56" spans="1:3">
-      <x:c r="A56" s="5"/>
-      <x:c r="C56" s="7"/>
+      <x:c r="A56" s="6"/>
+      <x:c r="C56" s="8"/>
     </x:row>
     <x:row r="57" spans="1:3">
-      <x:c r="A57" s="5"/>
-      <x:c r="B57" s="5"/>
-      <x:c r="C57" s="7"/>
+      <x:c r="A57" s="6"/>
+      <x:c r="B57" s="6"/>
+      <x:c r="C57" s="8"/>
     </x:row>
     <x:row r="58" spans="1:2">
-      <x:c r="A58" s="5"/>
-      <x:c r="B58" s="5"/>
-    </x:row>
-    <x:row r="59" spans="1:3" s="2" customFormat="1">
-      <x:c r="A59" s="5"/>
-      <x:c r="B59" s="5"/>
-      <x:c r="C59" s="7"/>
+      <x:c r="A58" s="6"/>
+      <x:c r="B58" s="6"/>
+    </x:row>
+    <x:row r="59" spans="1:3" s="3" customFormat="1">
+      <x:c r="A59" s="6"/>
+      <x:c r="B59" s="6"/>
+      <x:c r="C59" s="8"/>
     </x:row>
     <x:row r="60" spans="1:3">
-      <x:c r="A60" s="5"/>
-      <x:c r="B60" s="5"/>
-      <x:c r="C60" s="7"/>
+      <x:c r="A60" s="6"/>
+      <x:c r="B60" s="6"/>
+      <x:c r="C60" s="8"/>
     </x:row>
     <x:row r="61" spans="1:2">
-      <x:c r="A61" s="5"/>
-      <x:c r="B61" s="5"/>
+      <x:c r="A61" s="6"/>
+      <x:c r="B61" s="6"/>
     </x:row>
     <x:row r="62" spans="1:3">
-      <x:c r="A62" s="5"/>
-      <x:c r="B62" s="5"/>
-      <x:c r="C62" s="7"/>
+      <x:c r="A62" s="6"/>
+      <x:c r="B62" s="6"/>
+      <x:c r="C62" s="8"/>
     </x:row>
     <x:row r="63" spans="1:2">
-      <x:c r="A63" s="5"/>
-      <x:c r="B63" s="5"/>
+      <x:c r="A63" s="6"/>
+      <x:c r="B63" s="6"/>
     </x:row>
     <x:row r="64" spans="1:3">
-      <x:c r="A64" s="5"/>
-      <x:c r="B64" s="5"/>
-      <x:c r="C64" s="7"/>
+      <x:c r="A64" s="6"/>
+      <x:c r="B64" s="6"/>
+      <x:c r="C64" s="8"/>
     </x:row>
     <x:row r="65" spans="1:3">
-      <x:c r="A65" s="5"/>
-      <x:c r="B65" s="5"/>
-      <x:c r="C65" s="7"/>
+      <x:c r="A65" s="6"/>
+      <x:c r="B65" s="6"/>
+      <x:c r="C65" s="8"/>
     </x:row>
     <x:row r="66" spans="1:3">
-      <x:c r="A66" s="5"/>
-      <x:c r="B66" s="5"/>
-      <x:c r="C66" s="7"/>
+      <x:c r="A66" s="6"/>
+      <x:c r="B66" s="6"/>
+      <x:c r="C66" s="8"/>
     </x:row>
     <x:row r="67" spans="1:2">
-      <x:c r="A67" s="5"/>
-      <x:c r="B67" s="5"/>
+      <x:c r="A67" s="6"/>
+      <x:c r="B67" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
